--- a/training_schedule.xlsx
+++ b/training_schedule.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="27231"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="27726"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Ron Tohar\Desktop\הכשרה\CV_training\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B798172C-17C8-4D3F-BB91-D5C4702338A0}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{334DEF52-B4FA-4843-AEFE-55CE67488BFD}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-98" yWindow="-98" windowWidth="22695" windowHeight="14595" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="1103" yWindow="1103" windowWidth="16875" windowHeight="10522" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="גיליון1" sheetId="1" r:id="rId1"/>
@@ -36,7 +36,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="34" uniqueCount="32">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="33" uniqueCount="31">
   <si>
     <t>Topic</t>
   </si>
@@ -130,9 +130,6 @@
   </si>
   <si>
     <t>estimated time</t>
-  </si>
-  <si>
-    <t>skipped</t>
   </si>
 </sst>
 </file>
@@ -169,11 +166,12 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="2">
+  <cellXfs count="3">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment wrapText="1"/>
     </xf>
+    <xf numFmtId="16" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -454,12 +452,12 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:D31"/>
+  <dimension ref="A1:F31"/>
   <sheetFormatPr defaultRowHeight="13.5" x14ac:dyDescent="0.35"/>
   <cols>
-    <col min="1" max="1" width="26.9375" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="15.8125" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="12.8125" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="26.875" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="27.9375" customWidth="1"/>
+    <col min="3" max="3" width="16.125" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:4" x14ac:dyDescent="0.35">
@@ -486,7 +484,7 @@
       </c>
       <c r="D2">
         <f>SUM(D3)</f>
-        <v>0</v>
+        <v>0.5</v>
       </c>
     </row>
     <row r="3" spans="1:4" x14ac:dyDescent="0.35">
@@ -496,6 +494,9 @@
       <c r="C3">
         <v>0.5</v>
       </c>
+      <c r="D3">
+        <v>0.5</v>
+      </c>
     </row>
     <row r="5" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A5" t="s">
@@ -507,7 +508,7 @@
       </c>
       <c r="D5">
         <f>SUM(D6:D11)</f>
-        <v>2</v>
+        <v>18</v>
       </c>
     </row>
     <row r="6" spans="1:4" x14ac:dyDescent="0.35">
@@ -517,8 +518,8 @@
       <c r="C6">
         <v>1</v>
       </c>
-      <c r="D6" t="s">
-        <v>31</v>
+      <c r="D6">
+        <v>0</v>
       </c>
     </row>
     <row r="7" spans="1:4" x14ac:dyDescent="0.35">
@@ -539,6 +540,9 @@
       <c r="C8">
         <v>6.5</v>
       </c>
+      <c r="D8">
+        <v>6</v>
+      </c>
     </row>
     <row r="9" spans="1:4" x14ac:dyDescent="0.35">
       <c r="B9" t="s">
@@ -547,6 +551,9 @@
       <c r="C9">
         <v>1</v>
       </c>
+      <c r="D9">
+        <v>1.5</v>
+      </c>
     </row>
     <row r="10" spans="1:4" x14ac:dyDescent="0.35">
       <c r="B10" t="s">
@@ -555,6 +562,9 @@
       <c r="C10">
         <v>2</v>
       </c>
+      <c r="D10">
+        <v>2.5</v>
+      </c>
     </row>
     <row r="11" spans="1:4" x14ac:dyDescent="0.35">
       <c r="B11" t="s">
@@ -563,6 +573,9 @@
       <c r="C11">
         <v>3</v>
       </c>
+      <c r="D11">
+        <v>6</v>
+      </c>
     </row>
     <row r="12" spans="1:4" ht="27" x14ac:dyDescent="0.35">
       <c r="A12" s="1" t="s">
@@ -574,7 +587,7 @@
       </c>
       <c r="D12">
         <f>SUM(D13:D20)</f>
-        <v>0</v>
+        <v>14.5</v>
       </c>
     </row>
     <row r="13" spans="1:4" x14ac:dyDescent="0.35">
@@ -584,6 +597,9 @@
       <c r="C13">
         <v>1</v>
       </c>
+      <c r="D13">
+        <v>0.5</v>
+      </c>
     </row>
     <row r="14" spans="1:4" x14ac:dyDescent="0.35">
       <c r="B14" t="s">
@@ -592,6 +608,9 @@
       <c r="C14">
         <v>1</v>
       </c>
+      <c r="D14">
+        <v>0.5</v>
+      </c>
     </row>
     <row r="15" spans="1:4" x14ac:dyDescent="0.35">
       <c r="B15" t="s">
@@ -600,6 +619,9 @@
       <c r="C15">
         <v>1</v>
       </c>
+      <c r="D15">
+        <v>0.5</v>
+      </c>
     </row>
     <row r="16" spans="1:4" x14ac:dyDescent="0.35">
       <c r="B16" t="s">
@@ -608,40 +630,55 @@
       <c r="C16">
         <v>2</v>
       </c>
-    </row>
-    <row r="17" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="D16">
+        <v>1.5</v>
+      </c>
+    </row>
+    <row r="17" spans="1:6" x14ac:dyDescent="0.35">
       <c r="B17" t="s">
         <v>19</v>
       </c>
       <c r="C17">
         <v>2</v>
       </c>
-    </row>
-    <row r="18" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="D17">
+        <v>1.5</v>
+      </c>
+    </row>
+    <row r="18" spans="1:6" x14ac:dyDescent="0.35">
       <c r="B18" t="s">
         <v>20</v>
       </c>
       <c r="C18">
         <v>2</v>
       </c>
-    </row>
-    <row r="19" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="D18">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="19" spans="1:6" x14ac:dyDescent="0.35">
       <c r="B19" t="s">
         <v>21</v>
       </c>
       <c r="C19">
         <v>2</v>
       </c>
-    </row>
-    <row r="20" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="D19">
+        <v>4.5</v>
+      </c>
+    </row>
+    <row r="20" spans="1:6" x14ac:dyDescent="0.35">
       <c r="B20" t="s">
         <v>22</v>
       </c>
       <c r="C20">
         <v>2</v>
       </c>
-    </row>
-    <row r="21" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="D20">
+        <v>1.5</v>
+      </c>
+    </row>
+    <row r="21" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A21" t="s">
         <v>23</v>
       </c>
@@ -654,15 +691,21 @@
         <v>0</v>
       </c>
     </row>
-    <row r="22" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="22" spans="1:6" x14ac:dyDescent="0.35">
       <c r="B22" t="s">
         <v>24</v>
       </c>
       <c r="C22">
         <v>15</v>
       </c>
-    </row>
-    <row r="23" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="E22">
+        <v>5.5</v>
+      </c>
+      <c r="F22" s="2">
+        <v>45482</v>
+      </c>
+    </row>
+    <row r="23" spans="1:6" x14ac:dyDescent="0.35">
       <c r="B23" t="s">
         <v>25</v>
       </c>
@@ -670,7 +713,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="24" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="24" spans="1:6" x14ac:dyDescent="0.35">
       <c r="B24" t="s">
         <v>26</v>
       </c>
@@ -678,7 +721,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="25" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="25" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A25" t="s">
         <v>27</v>
       </c>
@@ -691,7 +734,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="26" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="26" spans="1:6" x14ac:dyDescent="0.35">
       <c r="B26" t="s">
         <v>24</v>
       </c>
@@ -699,7 +742,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="27" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="27" spans="1:6" x14ac:dyDescent="0.35">
       <c r="B27" t="s">
         <v>28</v>
       </c>
@@ -707,7 +750,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="28" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="28" spans="1:6" x14ac:dyDescent="0.35">
       <c r="B28" t="s">
         <v>29</v>
       </c>
@@ -715,7 +758,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="29" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="29" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A29" t="s">
         <v>1</v>
       </c>
@@ -728,12 +771,12 @@
         <v>0</v>
       </c>
     </row>
-    <row r="30" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="30" spans="1:6" x14ac:dyDescent="0.35">
       <c r="B30" t="s">
         <v>3</v>
       </c>
     </row>
-    <row r="31" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="31" spans="1:6" x14ac:dyDescent="0.35">
       <c r="B31" t="s">
         <v>5</v>
       </c>

--- a/training_schedule.xlsx
+++ b/training_schedule.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Ron Tohar\Desktop\הכשרה\CV_training\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{334DEF52-B4FA-4843-AEFE-55CE67488BFD}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E70F2322-2146-46A2-84E5-232A0B5749B2}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="1103" yWindow="1103" windowWidth="16875" windowHeight="10522" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-98" yWindow="-98" windowWidth="22695" windowHeight="14595" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="גיליון1" sheetId="1" r:id="rId1"/>
@@ -699,10 +699,10 @@
         <v>15</v>
       </c>
       <c r="E22">
-        <v>5.5</v>
+        <v>6.5</v>
       </c>
       <c r="F22" s="2">
-        <v>45482</v>
+        <v>45483</v>
       </c>
     </row>
     <row r="23" spans="1:6" x14ac:dyDescent="0.35">
